--- a/ct_scoop_links_2026-04-22.xlsx
+++ b/ct_scoop_links_2026-04-22.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,7 +440,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MILFORD SCOOP: O'Reilly Auto Parts bringing hub store to Milford</t>
+          <t>VERNON SCOOP: GNC closes at Tri-City Plaza</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
@@ -448,14 +448,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/milford-scoop-oreilly-auto-parts-bringing-hub-store-to-milford</t>
+          <t>https://www.theconnecticutscoop.com/all-tolland-county-posts/vernon-scoop-gnc-closes-at-tri-city-plaza</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHESHIRE SCOOP: Sephora sets opening date in Cheshire</t>
+          <t>SOMERS SCOOP: Roasted Beanery sets opening date!</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -463,14 +463,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/cheshire-scoop-sephora-sets-opening-date-in-cheshire</t>
+          <t>https://www.theconnecticutscoop.com/all-tolland-county-posts/somers-scoop-roasted-beanery-sets-opening-date</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WESTBROOK SCOOP: NYC restaurateurs bringing upscale Italian eatery to Shore Pub space!</t>
+          <t>MILFORD SCOOP: O'Reilly Auto Parts bringing hub store to Milford</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -478,14 +478,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-middlesex-county-posts/westbrook-scoop-nyc-restaurateurs-bringing-upscale-italian-eatery-to-shore-pub-space</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/milford-scoop-oreilly-auto-parts-bringing-hub-store-to-milford</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALLSTON SCOOP: Shinjuku Station Revolving Sushi coming soon to Allston.</t>
+          <t>CHESHIRE SCOOP: Sephora sets opening date in Cheshire</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
@@ -493,50 +493,110 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-mass-posts/allston-scoop-shinjuku-station-revolving-sushi-coming-soon-to-allston</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/cheshire-scoop-sephora-sets-opening-date-in-cheshire</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WEST HARTFORD SCOOP: Five new restaurants open in WeHa</t>
+          <t>STAMFORD SCOOP: Frank Pepe Pizzeria hosting free pizza party!</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/west-hartford-scoop-five-new-restaurants-open-in-weha</t>
+          <t>https://www.theconnecticutscoop.com/all-fairfield-county-posts/stamford-scoop-frank-pepe-pizzeria-hosting-free-pizza-party</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CANTON SCOOP: The Frosted Sheep Bake Shop sets opening date!</t>
+          <t>WESTBROOK SCOOP: NYC restaurateurs bringing upscale Italian eatery to Shore Pub space!</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/canton-scoop-the-frosted-sheep-bake-shop-sets-opening-date</t>
+          <t>https://www.theconnecticutscoop.com/all-middlesex-county-posts/westbrook-scoop-nyc-restaurateurs-bringing-upscale-italian-eatery-to-shore-pub-space</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>SPRINGFIELD SCOOP: Forman Mills coming soon to Springfield</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-mass-posts/springfield-scoop-forman-mills-coming-soon-to-springfield</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ALLSTON SCOOP: Shinjuku Station Revolving Sushi coming soon to Allston.</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-mass-posts/allston-scoop-shinjuku-station-revolving-sushi-coming-soon-to-allston</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WEST HARTFORD SCOOP: Five new restaurants open in WeHa</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/west-hartford-scoop-five-new-restaurants-open-in-weha</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CANTON SCOOP: The Frosted Sheep Bake Shop sets opening date!</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/canton-scoop-the-frosted-sheep-bake-shop-sets-opening-date</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>MILFORD SCOOP: Best Buy eyeing new Milford location</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B12" s="1" t="n">
         <v>46132</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/milford-scoop-best-buy-eyeing-new-milford-location</t>
         </is>
